--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/CI/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/CI/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingADV\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE9793E-AB10-4D2D-814A-11F484D5B08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEE2436-9DCB-4924-9D49-44DBB9C9CA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Dati originali</t>
   </si>
@@ -129,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,10 +138,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FFCCCCCC"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -164,11 +171,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -449,158 +458,182 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>13.166666666666666</v>
-      </c>
-      <c r="F3">
-        <v>0.76376261582597327</v>
-      </c>
-      <c r="G3">
-        <v>24.166666666666668</v>
-      </c>
-      <c r="H3">
-        <v>4.0104031385053265</v>
-      </c>
-      <c r="I3">
-        <v>28.833333333333332</v>
-      </c>
-      <c r="J3">
-        <v>4.3684474740270431</v>
-      </c>
-      <c r="K3">
-        <v>22.055555555555557</v>
-      </c>
-      <c r="L3">
-        <v>1.4561491580090185</v>
-      </c>
-      <c r="M3">
-        <v>8.8888888888888893</v>
-      </c>
-      <c r="N3">
-        <v>0.69388866648871195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C3" s="3">
+        <v>16.722222222222221</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.635231383473652</v>
+      </c>
+      <c r="E3" s="3">
+        <v>22.166666666666668</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5.2380817099392409</v>
+      </c>
+      <c r="G3" s="3">
+        <v>31.5</v>
+      </c>
+      <c r="H3" s="3">
+        <v>3.2691742076555053</v>
+      </c>
+      <c r="I3" s="3">
+        <v>23.462962962962958</v>
+      </c>
+      <c r="J3" s="3">
+        <v>2.8096779394544562</v>
+      </c>
+      <c r="K3" s="3">
+        <v>7.5740740740740744</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.90948364131916359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
         <v>17.125</v>
       </c>
-      <c r="F6">
+      <c r="D6" s="3">
         <v>3</v>
       </c>
-      <c r="G6">
+      <c r="E6" s="3">
         <v>22.166666666666668</v>
       </c>
-      <c r="H6">
+      <c r="F6" s="3">
         <v>2.0816659994661331</v>
       </c>
-      <c r="I6">
+      <c r="G6" s="3">
         <v>30.5</v>
       </c>
-      <c r="J6">
+      <c r="H6" s="3">
         <v>2</v>
       </c>
-      <c r="K6">
+      <c r="I6" s="3">
         <v>23.222222222222218</v>
       </c>
-      <c r="L6">
+      <c r="J6" s="3">
         <v>1.1706281947614148</v>
       </c>
-      <c r="M6">
+      <c r="K6" s="3">
         <v>6.2222222222222214</v>
       </c>
-      <c r="N6">
+      <c r="L6" s="3">
         <v>1.8358568490953682</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
         <v>15.25</v>
       </c>
-      <c r="F8">
+      <c r="D8" s="3">
         <v>5.3033008588991066</v>
       </c>
-      <c r="G8">
+      <c r="E8" s="3">
         <v>24.25</v>
       </c>
-      <c r="H8">
+      <c r="F8" s="3">
         <v>2.4748737341529163</v>
       </c>
-      <c r="I8">
+      <c r="G8" s="3">
         <v>28</v>
       </c>
-      <c r="J8">
+      <c r="H8" s="3">
         <v>1.4142135623730951</v>
       </c>
-      <c r="K8">
+      <c r="I8" s="3">
         <v>22.5</v>
       </c>
-      <c r="L8">
+      <c r="J8" s="3">
         <v>2.1213203435596424</v>
       </c>
-      <c r="M8">
+      <c r="K8" s="3">
         <v>7.25</v>
       </c>
-      <c r="N8">
+      <c r="L8" s="3">
         <v>3.1819805153394638</v>
       </c>
     </row>
@@ -612,7 +645,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="29" max="29" width="13.109375" customWidth="1"/>
@@ -678,22 +711,22 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
+        <v>87</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3">
         <v>85</v>
       </c>
-      <c r="C3">
-        <v>15</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>90</v>
-      </c>
       <c r="G3">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -702,204 +735,576 @@
         <v>94</v>
       </c>
       <c r="L3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="M3">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="N3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O3">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>20</v>
+        <v>21.5</v>
       </c>
       <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>20.833333333333332</v>
+        <v>20.5</v>
       </c>
       <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="V3">
         <f>T3-U3</f>
-        <v>8.3333333333333321</v>
+        <v>6.5</v>
       </c>
       <c r="W3">
-        <f>AVERAGE(Q3:Q5)</f>
-        <v>13.166666666666666</v>
+        <f>AVERAGE(Q3:Q11)</f>
+        <v>16.722222222222221</v>
       </c>
       <c r="X3">
-        <f>_xlfn.STDEV.S(Q3:Q5)</f>
-        <v>0.76376261582597327</v>
+        <f>_xlfn.STDEV.S(Q3:Q11)</f>
+        <v>2.635231383473652</v>
       </c>
       <c r="Y3">
-        <f>AVERAGE(R3:R5)</f>
-        <v>24.166666666666668</v>
+        <f>AVERAGE(R3:R11)</f>
+        <v>22.166666666666668</v>
       </c>
       <c r="Z3">
-        <f>_xlfn.STDEV.S(R3:R5)</f>
-        <v>4.0104031385053265</v>
+        <f>_xlfn.STDEV.S(R3:R11)</f>
+        <v>5.2380817099392409</v>
       </c>
       <c r="AA3">
-        <f>AVERAGE(S3:S5)</f>
-        <v>28.833333333333332</v>
+        <f>AVERAGE(S3:S11)</f>
+        <v>31.5</v>
       </c>
       <c r="AB3">
-        <f>_xlfn.STDEV.S(S3:S5)</f>
-        <v>4.3684474740270431</v>
+        <f>_xlfn.STDEV.S(S3:S11)</f>
+        <v>3.2691742076555053</v>
       </c>
       <c r="AC3">
-        <f>AVERAGE(T3:T5)</f>
-        <v>22.055555555555557</v>
+        <f>AVERAGE(T3:T11)</f>
+        <v>23.462962962962958</v>
       </c>
       <c r="AD3">
-        <f>_xlfn.STDEV.S(T3:T5)</f>
-        <v>1.4561491580090185</v>
+        <f>_xlfn.STDEV.S(T3:T11)</f>
+        <v>2.8096779394544562</v>
       </c>
       <c r="AE3">
-        <f>AVERAGE(V3:V5)</f>
-        <v>8.8888888888888893</v>
+        <f>AVERAGE(V3:V11)</f>
+        <v>7.5740740740740744</v>
       </c>
       <c r="AF3">
-        <f>_xlfn.STDEV.S(V3:V5)</f>
-        <v>0.69388866648871195</v>
+        <f>_xlfn.STDEV.S(V3:V11)</f>
+        <v>0.90948364131916359</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G4">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H4">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L4">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="M4">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="N4">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="O4">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="Q4">
         <f t="shared" ref="Q4:Q5" si="0">AVERAGE(C4:D4)</f>
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="R4">
         <f t="shared" ref="R4:R5" si="1">AVERAGE(H4:I4)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S4">
         <f t="shared" ref="S4:S5" si="2">AVERAGE(M4:N4)</f>
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="T4">
         <f t="shared" ref="T4:T5" si="3">AVERAGE(Q4:S4)</f>
-        <v>21.666666666666668</v>
+        <v>25.5</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
-        <v>8.6666666666666679</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G5">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H5">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L5">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M5">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N5">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="R5">
         <f t="shared" si="1"/>
-        <v>24.5</v>
+        <v>22.5</v>
       </c>
       <c r="S5">
         <f t="shared" si="2"/>
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="T5">
         <f t="shared" si="3"/>
-        <v>23.666666666666668</v>
+        <v>24</v>
       </c>
       <c r="U5">
         <f>MIN(Q5:S5)</f>
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="V5">
         <f>T5-U5</f>
-        <v>9.6666666666666679</v>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>79</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>78</v>
+      </c>
+      <c r="G6">
+        <v>52</v>
+      </c>
+      <c r="H6">
+        <v>48</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>94</v>
+      </c>
+      <c r="L6">
+        <v>64</v>
+      </c>
+      <c r="M6">
+        <v>36</v>
+      </c>
+      <c r="N6">
+        <v>40</v>
+      </c>
+      <c r="O6">
+        <v>60</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" ref="Q6:Q11" si="4">AVERAGE(C6:D6)</f>
+        <v>21.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" ref="R6:R11" si="5">AVERAGE(H6:I6)</f>
+        <v>27</v>
+      </c>
+      <c r="S6">
+        <f t="shared" ref="S6:S11" si="6">AVERAGE(M6:N6)</f>
+        <v>38</v>
+      </c>
+      <c r="T6">
+        <f t="shared" ref="T6:T11" si="7">AVERAGE(Q6:S6)</f>
+        <v>28.833333333333332</v>
+      </c>
+      <c r="U6">
+        <f t="shared" ref="U6:U11" si="8">MIN(Q6:S6)</f>
+        <v>21.5</v>
+      </c>
+      <c r="V6">
+        <f t="shared" ref="V6:V11" si="9">T6-U6</f>
+        <v>7.3333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>84</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>76</v>
+      </c>
+      <c r="G7">
+        <v>79</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>96</v>
+      </c>
+      <c r="L7">
+        <v>68</v>
+      </c>
+      <c r="M7">
+        <v>32</v>
+      </c>
+      <c r="N7">
+        <v>32</v>
+      </c>
+      <c r="O7">
+        <v>68</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="5"/>
+        <v>12.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="7"/>
+        <v>21.5</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="8"/>
+        <v>12.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>85</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>84</v>
+      </c>
+      <c r="G8">
+        <v>56</v>
+      </c>
+      <c r="H8">
+        <v>44</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>94</v>
+      </c>
+      <c r="L8">
+        <v>66</v>
+      </c>
+      <c r="M8">
+        <v>34</v>
+      </c>
+      <c r="N8">
+        <v>29</v>
+      </c>
+      <c r="O8">
+        <v>71</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="6"/>
+        <v>31.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="8"/>
+        <v>15.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="9"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>84</v>
+      </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>18</v>
+      </c>
+      <c r="E9">
+        <v>82</v>
+      </c>
+      <c r="G9">
+        <v>55</v>
+      </c>
+      <c r="H9">
+        <v>45</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>89</v>
+      </c>
+      <c r="L9">
+        <v>69</v>
+      </c>
+      <c r="M9">
+        <v>31</v>
+      </c>
+      <c r="N9">
+        <v>30</v>
+      </c>
+      <c r="O9">
+        <v>70</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="6"/>
+        <v>30.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="7"/>
+        <v>25.166666666666668</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="8"/>
+        <v>17</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="9"/>
+        <v>8.1666666666666679</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>88</v>
+      </c>
+      <c r="C10">
+        <v>12</v>
+      </c>
+      <c r="D10">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>84</v>
+      </c>
+      <c r="G10">
+        <v>70</v>
+      </c>
+      <c r="H10">
+        <v>30</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <v>92</v>
+      </c>
+      <c r="L10">
+        <v>63</v>
+      </c>
+      <c r="M10">
+        <v>37</v>
+      </c>
+      <c r="N10">
+        <v>20</v>
+      </c>
+      <c r="O10">
+        <v>80</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="6"/>
+        <v>28.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="7"/>
+        <v>20.5</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="9"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>87</v>
+      </c>
+      <c r="C11">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>84</v>
+      </c>
+      <c r="G11">
+        <v>70</v>
+      </c>
+      <c r="H11">
+        <v>30</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
+        <v>96</v>
+      </c>
+      <c r="L11">
+        <v>59</v>
+      </c>
+      <c r="M11">
+        <v>41</v>
+      </c>
+      <c r="N11">
+        <v>23</v>
+      </c>
+      <c r="O11">
+        <v>77</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="7"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="8"/>
+        <v>14.5</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="9"/>
+        <v>6.6666666666666679</v>
       </c>
     </row>
   </sheetData>
@@ -1696,19 +2101,19 @@
         <v>74</v>
       </c>
       <c r="Q16">
-        <f t="shared" ref="Q16:Q18" si="12">AVERAGE(C16:D16)</f>
+        <f t="shared" ref="Q16" si="12">AVERAGE(C16:D16)</f>
         <v>16</v>
       </c>
       <c r="R16">
-        <f t="shared" ref="R16:R18" si="13">AVERAGE(H16:I16)</f>
+        <f t="shared" ref="R16" si="13">AVERAGE(H16:I16)</f>
         <v>28.5</v>
       </c>
       <c r="S16">
-        <f t="shared" ref="S16:S18" si="14">AVERAGE(M16:N16)</f>
+        <f t="shared" ref="S16" si="14">AVERAGE(M16:N16)</f>
         <v>31.5</v>
       </c>
       <c r="T16">
-        <f t="shared" ref="T16:T18" si="15">AVERAGE(Q16:S16)</f>
+        <f t="shared" ref="T16" si="15">AVERAGE(Q16:S16)</f>
         <v>25.333333333333332</v>
       </c>
       <c r="U16">

--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/CI/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/CI/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingADV\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEE2436-9DCB-4924-9D49-44DBB9C9CA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4CED8B-9059-4753-A854-F176D85B3D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>Dati originali</t>
   </si>
@@ -117,12 +117,6 @@
   </si>
   <si>
     <t>NOCLSDIV</t>
-  </si>
-  <si>
-    <t>eps=0.001</t>
-  </si>
-  <si>
-    <t>eps=0.01</t>
   </si>
 </sst>
 </file>
@@ -560,34 +554,34 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
-        <v>17.125</v>
+        <v>15.5</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2.4494897427831779</v>
       </c>
       <c r="E6" s="3">
-        <v>22.166666666666668</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3">
-        <v>2.0816659994661331</v>
+        <v>2.5495097567963922</v>
       </c>
       <c r="G6" s="3">
-        <v>30.5</v>
+        <v>31.416666666666668</v>
       </c>
       <c r="H6" s="3">
-        <v>2</v>
+        <v>3.9801591257971842</v>
       </c>
       <c r="I6" s="3">
-        <v>23.222222222222218</v>
+        <v>22.305555555555554</v>
       </c>
       <c r="J6" s="3">
-        <v>1.1706281947614148</v>
+        <v>2.0423751605168672</v>
       </c>
       <c r="K6" s="3">
-        <v>6.2222222222222214</v>
+        <v>7.1388888888888884</v>
       </c>
       <c r="L6" s="3">
-        <v>1.8358568490953682</v>
+        <v>1.7493384993148686</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -607,34 +601,34 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
-        <v>15.25</v>
+        <v>14.416666666666666</v>
       </c>
       <c r="D8" s="3">
-        <v>5.3033008588991066</v>
+        <v>1.6253204812179816</v>
       </c>
       <c r="E8" s="3">
-        <v>24.25</v>
+        <v>20.666666666666668</v>
       </c>
       <c r="F8" s="3">
-        <v>2.4748737341529163</v>
+        <v>4.1793141383086647</v>
       </c>
       <c r="G8" s="3">
-        <v>28</v>
+        <v>28.916666666666668</v>
       </c>
       <c r="H8" s="3">
-        <v>1.4142135623730951</v>
+        <v>4.7161071517371829</v>
       </c>
       <c r="I8" s="3">
-        <v>22.5</v>
+        <v>21.333333333333332</v>
       </c>
       <c r="J8" s="3">
-        <v>2.1213203435596424</v>
+        <v>2.4312776705080856</v>
       </c>
       <c r="K8" s="3">
-        <v>7.25</v>
+        <v>7.3333333333333313</v>
       </c>
       <c r="L8" s="3">
-        <v>3.1819805153394638</v>
+        <v>3.0785999704050244</v>
       </c>
     </row>
   </sheetData>
@@ -1315,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
-  <dimension ref="A2:AF16"/>
+  <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="28" max="28" width="12.21875" customWidth="1"/>
@@ -1377,752 +1371,414 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B3">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G3">
+        <v>67</v>
+      </c>
+      <c r="H3">
+        <v>33</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>91</v>
+      </c>
+      <c r="L3">
         <v>69</v>
       </c>
-      <c r="H3">
+      <c r="M3">
         <v>31</v>
       </c>
-      <c r="I3">
-        <v>10</v>
-      </c>
-      <c r="J3">
-        <v>90</v>
-      </c>
-      <c r="L3">
-        <v>66</v>
-      </c>
-      <c r="M3">
-        <v>34</v>
-      </c>
       <c r="N3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="O3">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>32.5</v>
+        <v>28.5</v>
       </c>
       <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>23.333333333333332</v>
+        <v>21.5</v>
       </c>
       <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V3">
         <f>T3-U3</f>
-        <v>6.3333333333333321</v>
+        <v>6.5</v>
       </c>
       <c r="W3">
-        <f>AVERAGE(Q3:Q6)</f>
-        <v>17.125</v>
+        <f>AVERAGE(Q3:Q8)</f>
+        <v>15.5</v>
       </c>
       <c r="X3">
-        <f>_xlfn.STDEV.S(Q3:Q5)</f>
-        <v>3</v>
+        <f>_xlfn.STDEV.S(Q3:Q8)</f>
+        <v>2.4494897427831779</v>
       </c>
       <c r="Y3">
-        <f>AVERAGE(R3:R5)</f>
-        <v>22.166666666666668</v>
+        <f>AVERAGE(R3:R8)</f>
+        <v>20</v>
       </c>
       <c r="Z3">
-        <f>_xlfn.STDEV.S(R3:R5)</f>
-        <v>2.0816659994661331</v>
+        <f>_xlfn.STDEV.S(R3:R8)</f>
+        <v>2.5495097567963922</v>
       </c>
       <c r="AA3">
-        <f>AVERAGE(S3:S5)</f>
-        <v>30.5</v>
+        <f>AVERAGE(S3:S8)</f>
+        <v>31.416666666666668</v>
       </c>
       <c r="AB3">
-        <f>_xlfn.STDEV.S(S3:S5)</f>
-        <v>2</v>
+        <f>_xlfn.STDEV.S(S3:S8)</f>
+        <v>3.9801591257971842</v>
       </c>
       <c r="AC3">
-        <f>AVERAGE(T3:T5)</f>
-        <v>23.222222222222218</v>
+        <f>AVERAGE(T3:T8)</f>
+        <v>22.305555555555554</v>
       </c>
       <c r="AD3">
-        <f>_xlfn.STDEV.S(T3:T5)</f>
-        <v>1.1706281947614148</v>
+        <f>_xlfn.STDEV.S(T3:T8)</f>
+        <v>2.0423751605168672</v>
       </c>
       <c r="AE3">
-        <f>AVERAGE(V3:V5)</f>
-        <v>6.2222222222222214</v>
+        <f>AVERAGE(V3:V8)</f>
+        <v>7.1388888888888884</v>
       </c>
       <c r="AF3">
-        <f>_xlfn.STDEV.S(V3:V5)</f>
-        <v>1.8358568490953682</v>
+        <f>_xlfn.STDEV.S(V3:V8)</f>
+        <v>1.7493384993148686</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
+        <v>83</v>
+      </c>
+      <c r="C4">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>83</v>
+      </c>
+      <c r="G4">
+        <v>75</v>
+      </c>
+      <c r="H4">
+        <v>25</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>95</v>
+      </c>
+      <c r="L4">
+        <v>60</v>
+      </c>
+      <c r="M4">
+        <v>40</v>
+      </c>
+      <c r="N4">
+        <v>15</v>
+      </c>
+      <c r="O4">
         <v>85</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-      <c r="D4">
-        <v>13</v>
-      </c>
-      <c r="E4">
-        <v>87</v>
-      </c>
-      <c r="G4">
-        <v>66</v>
-      </c>
-      <c r="H4">
-        <v>34</v>
-      </c>
-      <c r="I4">
-        <v>9</v>
-      </c>
-      <c r="J4">
-        <v>91</v>
-      </c>
-      <c r="L4">
-        <v>62</v>
-      </c>
-      <c r="M4">
-        <v>38</v>
-      </c>
-      <c r="N4">
-        <v>23</v>
-      </c>
-      <c r="O4">
-        <v>77</v>
       </c>
       <c r="Q4">
         <f t="shared" ref="Q4:Q5" si="0">AVERAGE(C4:D4)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R4">
         <f t="shared" ref="R4:R5" si="1">AVERAGE(H4:I4)</f>
-        <v>21.5</v>
+        <v>15</v>
       </c>
       <c r="S4">
         <f t="shared" ref="S4:S5" si="2">AVERAGE(M4:N4)</f>
-        <v>30.5</v>
+        <v>27.5</v>
       </c>
       <c r="T4">
         <f t="shared" ref="T4:T5" si="3">AVERAGE(Q4:S4)</f>
-        <v>22</v>
+        <v>19.833333333333332</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
-        <v>8</v>
+        <v>4.8333333333333321</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B5">
+        <v>74</v>
+      </c>
+      <c r="C5">
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>87</v>
+      </c>
+      <c r="G5">
+        <v>63</v>
+      </c>
+      <c r="H5">
+        <v>37</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>94</v>
+      </c>
+      <c r="L5">
+        <v>48</v>
+      </c>
+      <c r="M5">
+        <v>52</v>
+      </c>
+      <c r="N5">
+        <v>17</v>
+      </c>
+      <c r="O5">
         <v>83</v>
-      </c>
-      <c r="C5">
-        <v>17</v>
-      </c>
-      <c r="D5">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>77</v>
-      </c>
-      <c r="G5">
-        <v>59</v>
-      </c>
-      <c r="H5">
-        <v>41</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>92</v>
-      </c>
-      <c r="L5">
-        <v>66</v>
-      </c>
-      <c r="M5">
-        <v>34</v>
-      </c>
-      <c r="N5">
-        <v>23</v>
-      </c>
-      <c r="O5">
-        <v>77</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="R5">
         <f t="shared" si="1"/>
-        <v>24.5</v>
+        <v>21.5</v>
       </c>
       <c r="S5">
         <f t="shared" si="2"/>
-        <v>28.5</v>
+        <v>34.5</v>
       </c>
       <c r="T5">
         <f t="shared" si="3"/>
-        <v>24.333333333333332</v>
+        <v>25.166666666666668</v>
       </c>
       <c r="U5">
         <f>MIN(Q5:S5)</f>
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="V5">
         <f>T5-U5</f>
-        <v>4.3333333333333321</v>
+        <v>5.6666666666666679</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G6">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L6">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M6">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N6">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="O6">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="Q6">
         <f t="shared" ref="Q6" si="4">AVERAGE(C6:D6)</f>
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="R6">
         <f t="shared" ref="R6" si="5">AVERAGE(H6:I6)</f>
-        <v>16.5</v>
+        <v>20.5</v>
       </c>
       <c r="S6">
         <f t="shared" ref="S6" si="6">AVERAGE(M6:N6)</f>
-        <v>27</v>
+        <v>37.5</v>
       </c>
       <c r="T6">
         <f t="shared" ref="T6" si="7">AVERAGE(Q6:S6)</f>
-        <v>20.333333333333332</v>
+        <v>24.333333333333332</v>
       </c>
       <c r="U6">
         <f>MIN(Q6:S6)</f>
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="V6">
         <f>T6-U6</f>
-        <v>3.8333333333333321</v>
+        <v>9.3333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>87</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>88</v>
+      </c>
+      <c r="G7">
+        <v>63</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>93</v>
+      </c>
+      <c r="L7">
+        <v>65</v>
+      </c>
+      <c r="M7">
+        <v>35</v>
+      </c>
+      <c r="N7">
+        <v>22</v>
+      </c>
+      <c r="O7">
+        <v>78</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" ref="Q7:Q8" si="8">AVERAGE(C7:D7)</f>
+        <v>12.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" ref="R7:R8" si="9">AVERAGE(H7:I7)</f>
+        <v>22</v>
+      </c>
+      <c r="S7">
+        <f t="shared" ref="S7:S8" si="10">AVERAGE(M7:N7)</f>
+        <v>28.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" ref="T7:T8" si="11">AVERAGE(Q7:S7)</f>
+        <v>21</v>
+      </c>
+      <c r="U7">
+        <f t="shared" ref="U7:U8" si="12">MIN(Q7:S7)</f>
+        <v>12.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" ref="V7:V8" si="13">T7-U7</f>
+        <v>8.5</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>85</v>
-      </c>
-      <c r="C9">
-        <v>15</v>
-      </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
-      <c r="E9">
-        <v>85</v>
-      </c>
-      <c r="G9">
-        <v>64</v>
-      </c>
-      <c r="H9">
-        <v>36</v>
-      </c>
-      <c r="I9">
+      <c r="B8">
+        <v>79</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>93</v>
+      </c>
+      <c r="G8">
+        <v>62</v>
+      </c>
+      <c r="H8">
+        <v>38</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>98</v>
+      </c>
+      <c r="L8">
+        <v>49</v>
+      </c>
+      <c r="M8">
+        <v>51</v>
+      </c>
+      <c r="N8">
+        <v>13</v>
+      </c>
+      <c r="O8">
+        <v>87</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="10"/>
+        <v>32</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="11"/>
+        <v>22</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="13"/>
         <v>8</v>
-      </c>
-      <c r="J9">
-        <v>92</v>
-      </c>
-      <c r="L9">
-        <v>66</v>
-      </c>
-      <c r="M9">
-        <v>34</v>
-      </c>
-      <c r="N9">
-        <v>33</v>
-      </c>
-      <c r="O9">
-        <v>67</v>
-      </c>
-      <c r="Q9">
-        <f>AVERAGE(C9:D9)</f>
-        <v>15</v>
-      </c>
-      <c r="R9">
-        <f>AVERAGE(H9:I9)</f>
-        <v>22</v>
-      </c>
-      <c r="S9">
-        <f>AVERAGE(M9:N9)</f>
-        <v>33.5</v>
-      </c>
-      <c r="T9">
-        <f>AVERAGE(Q9:S9)</f>
-        <v>23.5</v>
-      </c>
-      <c r="U9">
-        <f>MIN(Q9:S9)</f>
-        <v>15</v>
-      </c>
-      <c r="V9">
-        <f>T9-U9</f>
-        <v>8.5</v>
-      </c>
-      <c r="W9">
-        <f>AVERAGE(Q9:Q12)</f>
-        <v>16.75</v>
-      </c>
-      <c r="X9">
-        <f>_xlfn.STDEV.S(Q9:Q11)</f>
-        <v>2.5166114784235796</v>
-      </c>
-      <c r="Y9">
-        <f>AVERAGE(R9:R11)</f>
-        <v>26</v>
-      </c>
-      <c r="Z9">
-        <f>_xlfn.STDEV.S(R9:R11)</f>
-        <v>3.6055512754639891</v>
-      </c>
-      <c r="AA9">
-        <f>AVERAGE(S9:S11)</f>
-        <v>32.5</v>
-      </c>
-      <c r="AB9">
-        <f>_xlfn.STDEV.S(S9:S11)</f>
-        <v>1</v>
-      </c>
-      <c r="AC9">
-        <f>AVERAGE(T9:T11)</f>
-        <v>24.611111111111111</v>
-      </c>
-      <c r="AD9">
-        <f>_xlfn.STDEV.S(T9:T11)</f>
-        <v>1.0183501544346309</v>
-      </c>
-      <c r="AE9">
-        <f>AVERAGE(V9:V11)</f>
-        <v>9.2777777777777768</v>
-      </c>
-      <c r="AF9">
-        <f>_xlfn.STDEV.S(V9:V11)</f>
-        <v>2.2689530951846764</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>84</v>
-      </c>
-      <c r="C10">
-        <v>16</v>
-      </c>
-      <c r="D10">
-        <v>20</v>
-      </c>
-      <c r="E10">
-        <v>80</v>
-      </c>
-      <c r="G10">
-        <v>53</v>
-      </c>
-      <c r="H10">
-        <v>47</v>
-      </c>
-      <c r="I10">
-        <v>7</v>
-      </c>
-      <c r="J10">
-        <v>93</v>
-      </c>
-      <c r="L10">
-        <v>52</v>
-      </c>
-      <c r="M10">
-        <v>48</v>
-      </c>
-      <c r="N10">
-        <v>15</v>
-      </c>
-      <c r="O10">
-        <v>85</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" ref="Q10:Q12" si="8">AVERAGE(C10:D10)</f>
-        <v>18</v>
-      </c>
-      <c r="R10">
-        <f t="shared" ref="R10:R12" si="9">AVERAGE(H10:I10)</f>
-        <v>27</v>
-      </c>
-      <c r="S10">
-        <f t="shared" ref="S10:S12" si="10">AVERAGE(M10:N10)</f>
-        <v>31.5</v>
-      </c>
-      <c r="T10">
-        <f t="shared" ref="T10:T12" si="11">AVERAGE(Q10:S10)</f>
-        <v>25.5</v>
-      </c>
-      <c r="U10">
-        <f>MIN(Q10:S10)</f>
-        <v>18</v>
-      </c>
-      <c r="V10">
-        <f>T10-U10</f>
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>84</v>
-      </c>
-      <c r="C11">
-        <v>16</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-      <c r="E11">
-        <v>90</v>
-      </c>
-      <c r="G11">
-        <v>53</v>
-      </c>
-      <c r="H11">
-        <v>47</v>
-      </c>
-      <c r="I11">
-        <v>11</v>
-      </c>
-      <c r="J11">
-        <v>89</v>
-      </c>
-      <c r="L11">
-        <v>62</v>
-      </c>
-      <c r="M11">
-        <v>38</v>
-      </c>
-      <c r="N11">
-        <v>27</v>
-      </c>
-      <c r="O11">
-        <v>73</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="9"/>
-        <v>29</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="10"/>
-        <v>32.5</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="11"/>
-        <v>24.833333333333332</v>
-      </c>
-      <c r="U11">
-        <f>MIN(Q11:S11)</f>
-        <v>13</v>
-      </c>
-      <c r="V11">
-        <f>T11-U11</f>
-        <v>11.833333333333332</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>80</v>
-      </c>
-      <c r="C12">
-        <v>20</v>
-      </c>
-      <c r="D12">
-        <v>22</v>
-      </c>
-      <c r="E12">
-        <v>78</v>
-      </c>
-      <c r="G12">
-        <v>54</v>
-      </c>
-      <c r="H12">
-        <v>46</v>
-      </c>
-      <c r="I12">
-        <v>8</v>
-      </c>
-      <c r="J12">
-        <v>92</v>
-      </c>
-      <c r="L12">
-        <v>63</v>
-      </c>
-      <c r="M12">
-        <v>37</v>
-      </c>
-      <c r="N12">
-        <v>39</v>
-      </c>
-      <c r="O12">
-        <v>61</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="9"/>
-        <v>27</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="10"/>
-        <v>38</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="11"/>
-        <v>28.666666666666668</v>
-      </c>
-      <c r="U12">
-        <f>MIN(Q12:S12)</f>
-        <v>21</v>
-      </c>
-      <c r="V12">
-        <f>T12-U12</f>
-        <v>7.6666666666666679</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>78</v>
-      </c>
-      <c r="C15">
-        <v>22</v>
-      </c>
-      <c r="D15">
-        <v>21</v>
-      </c>
-      <c r="E15">
-        <v>79</v>
-      </c>
-      <c r="G15">
-        <v>72</v>
-      </c>
-      <c r="H15">
-        <v>28</v>
-      </c>
-      <c r="I15">
-        <v>6</v>
-      </c>
-      <c r="J15">
-        <v>94</v>
-      </c>
-      <c r="L15">
-        <v>67</v>
-      </c>
-      <c r="M15">
-        <v>33</v>
-      </c>
-      <c r="N15">
-        <v>33</v>
-      </c>
-      <c r="O15">
-        <v>67</v>
-      </c>
-      <c r="Q15">
-        <f>AVERAGE(C15:D15)</f>
-        <v>21.5</v>
-      </c>
-      <c r="R15">
-        <f>AVERAGE(H15:I15)</f>
-        <v>17</v>
-      </c>
-      <c r="S15">
-        <f>AVERAGE(M15:N15)</f>
-        <v>33</v>
-      </c>
-      <c r="T15">
-        <f>AVERAGE(Q15:S15)</f>
-        <v>23.833333333333332</v>
-      </c>
-      <c r="U15">
-        <f>MIN(Q15:S15)</f>
-        <v>17</v>
-      </c>
-      <c r="V15">
-        <f>T15-U15</f>
-        <v>6.8333333333333321</v>
-      </c>
-      <c r="W15">
-        <f>AVERAGE(Q15:Q18)</f>
-        <v>18.75</v>
-      </c>
-      <c r="X15">
-        <f>_xlfn.STDEV.S(Q15:Q17)</f>
-        <v>3.8890872965260113</v>
-      </c>
-      <c r="Y15">
-        <f>AVERAGE(R15:R17)</f>
-        <v>22.75</v>
-      </c>
-      <c r="Z15">
-        <f>_xlfn.STDEV.S(R15:R17)</f>
-        <v>8.1317279836452965</v>
-      </c>
-      <c r="AA15">
-        <f>AVERAGE(S15:S17)</f>
-        <v>32.25</v>
-      </c>
-      <c r="AB15">
-        <f>_xlfn.STDEV.S(S15:S17)</f>
-        <v>1.0606601717798212</v>
-      </c>
-      <c r="AC15">
-        <f>AVERAGE(T15:T17)</f>
-        <v>24.583333333333332</v>
-      </c>
-      <c r="AD15">
-        <f>_xlfn.STDEV.S(T15:T17)</f>
-        <v>1.0606601717798212</v>
-      </c>
-      <c r="AE15">
-        <f>AVERAGE(V15:V17)</f>
-        <v>8.0833333333333321</v>
-      </c>
-      <c r="AF15">
-        <f>_xlfn.STDEV.S(V15:V17)</f>
-        <v>1.7677669529663689</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B16">
-        <v>81</v>
-      </c>
-      <c r="C16">
-        <v>19</v>
-      </c>
-      <c r="D16">
-        <v>13</v>
-      </c>
-      <c r="E16">
-        <v>87</v>
-      </c>
-      <c r="G16">
-        <v>50</v>
-      </c>
-      <c r="H16">
-        <v>50</v>
-      </c>
-      <c r="I16">
-        <v>7</v>
-      </c>
-      <c r="J16">
-        <v>93</v>
-      </c>
-      <c r="L16">
-        <v>63</v>
-      </c>
-      <c r="M16">
-        <v>37</v>
-      </c>
-      <c r="N16">
-        <v>26</v>
-      </c>
-      <c r="O16">
-        <v>74</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" ref="Q16" si="12">AVERAGE(C16:D16)</f>
-        <v>16</v>
-      </c>
-      <c r="R16">
-        <f t="shared" ref="R16" si="13">AVERAGE(H16:I16)</f>
-        <v>28.5</v>
-      </c>
-      <c r="S16">
-        <f t="shared" ref="S16" si="14">AVERAGE(M16:N16)</f>
-        <v>31.5</v>
-      </c>
-      <c r="T16">
-        <f t="shared" ref="T16" si="15">AVERAGE(Q16:S16)</f>
-        <v>25.333333333333332</v>
-      </c>
-      <c r="U16">
-        <f>MIN(Q16:S16)</f>
-        <v>16</v>
-      </c>
-      <c r="V16">
-        <f>T16-U16</f>
-        <v>9.3333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -2132,7 +1788,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E62EF1-0098-48B1-8405-A4F0E6569F16}">
-  <dimension ref="A2:AF16"/>
+  <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -2190,752 +1846,414 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B3">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L3">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>25.666666666666668</v>
+        <v>21.166666666666668</v>
       </c>
       <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="V3">
         <f>T3-U3</f>
-        <v>4.6666666666666679</v>
+        <v>8.1666666666666679</v>
       </c>
       <c r="W3">
-        <f>AVERAGE(Q3:Q6)</f>
-        <v>18.75</v>
+        <f>AVERAGE(Q3:Q8)</f>
+        <v>14.416666666666666</v>
       </c>
       <c r="X3">
-        <f>_xlfn.STDEV.S(Q3:Q5)</f>
-        <v>1.5275252316519465</v>
+        <f>_xlfn.STDEV.S(Q3:Q8)</f>
+        <v>1.6253204812179816</v>
       </c>
       <c r="Y3">
-        <f>AVERAGE(R3:R5)</f>
-        <v>20.833333333333332</v>
+        <f>AVERAGE(R3:R8)</f>
+        <v>20.666666666666668</v>
       </c>
       <c r="Z3">
-        <f>_xlfn.STDEV.S(R3:R5)</f>
-        <v>1.7559422921421231</v>
+        <f>_xlfn.STDEV.S(R3:R8)</f>
+        <v>4.1793141383086647</v>
       </c>
       <c r="AA3">
-        <f>AVERAGE(S3:S5)</f>
-        <v>34.5</v>
+        <f>AVERAGE(S3:S8)</f>
+        <v>28.916666666666668</v>
       </c>
       <c r="AB3">
-        <f>_xlfn.STDEV.S(S3:S5)</f>
-        <v>3.7749172176353749</v>
+        <f>_xlfn.STDEV.S(S3:S8)</f>
+        <v>4.7161071517371829</v>
       </c>
       <c r="AC3">
-        <f>AVERAGE(T3:T5)</f>
-        <v>25.333333333333332</v>
+        <f>AVERAGE(T3:T8)</f>
+        <v>21.333333333333332</v>
       </c>
       <c r="AD3">
-        <f>_xlfn.STDEV.S(T3:T5)</f>
-        <v>1.2018504251546629</v>
+        <f>_xlfn.STDEV.S(T3:T8)</f>
+        <v>2.4312776705080856</v>
       </c>
       <c r="AE3">
-        <f>AVERAGE(V3:V5)</f>
-        <v>5.666666666666667</v>
+        <f>AVERAGE(V3:V8)</f>
+        <v>7.3333333333333313</v>
       </c>
       <c r="AF3">
-        <f>_xlfn.STDEV.S(V3:V5)</f>
-        <v>1.4529663145135565</v>
+        <f>_xlfn.STDEV.S(V3:V8)</f>
+        <v>3.0785999704050244</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
+        <v>82</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>94</v>
+      </c>
+      <c r="G4">
+        <v>58</v>
+      </c>
+      <c r="H4">
+        <v>42</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>93</v>
+      </c>
+      <c r="L4">
+        <v>53</v>
+      </c>
+      <c r="M4">
+        <v>47</v>
+      </c>
+      <c r="N4">
+        <v>27</v>
+      </c>
+      <c r="O4">
         <v>73</v>
-      </c>
-      <c r="C4">
-        <v>27</v>
-      </c>
-      <c r="D4">
-        <v>17</v>
-      </c>
-      <c r="E4">
-        <v>83</v>
-      </c>
-      <c r="G4">
-        <v>68</v>
-      </c>
-      <c r="H4">
-        <v>32</v>
-      </c>
-      <c r="I4">
-        <v>6</v>
-      </c>
-      <c r="J4">
-        <v>94</v>
-      </c>
-      <c r="L4">
-        <v>48</v>
-      </c>
-      <c r="M4">
-        <v>52</v>
-      </c>
-      <c r="N4">
-        <v>24</v>
-      </c>
-      <c r="O4">
-        <v>76</v>
       </c>
       <c r="Q4">
         <f t="shared" ref="Q4:Q6" si="0">AVERAGE(C4:D4)</f>
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="R4">
         <f t="shared" ref="R4:R6" si="1">AVERAGE(H4:I4)</f>
-        <v>19</v>
+        <v>24.5</v>
       </c>
       <c r="S4">
         <f t="shared" ref="S4:S6" si="2">AVERAGE(M4:N4)</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T4">
         <f t="shared" ref="T4:T6" si="3">AVERAGE(Q4:S4)</f>
-        <v>26.333333333333332</v>
+        <v>24.5</v>
       </c>
       <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V4">
         <f>T4-U4</f>
-        <v>7.3333333333333321</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G5">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L5">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="N5">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="R5">
         <f t="shared" si="1"/>
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="S5">
         <f t="shared" si="2"/>
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="T5">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>22.833333333333332</v>
       </c>
       <c r="U5">
         <f>MIN(Q5:S5)</f>
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="V5">
         <f>T5-U5</f>
-        <v>5</v>
+        <v>8.3333333333333321</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G6">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H6">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L6">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="M6">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="N6">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R6">
         <f t="shared" si="1"/>
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="S6">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
-        <v>20.166666666666668</v>
+        <v>17.833333333333332</v>
       </c>
       <c r="U6">
         <f>MIN(Q6:S6)</f>
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="V6">
         <f>T6-U6</f>
-        <v>7.1666666666666679</v>
+        <v>4.3333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>77</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>91</v>
+      </c>
+      <c r="G7">
+        <v>57</v>
+      </c>
+      <c r="H7">
+        <v>43</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>96</v>
+      </c>
+      <c r="L7">
+        <v>72</v>
+      </c>
+      <c r="M7">
+        <v>28</v>
+      </c>
+      <c r="N7">
+        <v>27</v>
+      </c>
+      <c r="O7">
+        <v>73</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" ref="Q7:Q8" si="4">AVERAGE(C7:D7)</f>
+        <v>16</v>
+      </c>
+      <c r="R7">
+        <f t="shared" ref="R7:R8" si="5">AVERAGE(H7:I7)</f>
+        <v>23.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" ref="S7:S8" si="6">AVERAGE(M7:N7)</f>
+        <v>27.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" ref="T7:T8" si="7">AVERAGE(Q7:S7)</f>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U7">
+        <f t="shared" ref="U7:U8" si="8">MIN(Q7:S7)</f>
+        <v>16</v>
+      </c>
+      <c r="V7">
+        <f t="shared" ref="V7:V8" si="9">T7-U7</f>
+        <v>6.3333333333333321</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>76</v>
-      </c>
-      <c r="C9">
-        <v>24</v>
-      </c>
-      <c r="D9">
-        <v>17</v>
-      </c>
-      <c r="E9">
-        <v>83</v>
-      </c>
-      <c r="G9">
-        <v>72</v>
-      </c>
-      <c r="H9">
-        <v>28</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>90</v>
-      </c>
-      <c r="L9">
-        <v>65</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
-      </c>
-      <c r="N9">
-        <v>27</v>
-      </c>
-      <c r="O9">
-        <v>73</v>
-      </c>
-      <c r="Q9">
-        <f>AVERAGE(C9:D9)</f>
-        <v>20.5</v>
-      </c>
-      <c r="R9">
-        <f>AVERAGE(H9:I9)</f>
-        <v>19</v>
-      </c>
-      <c r="S9">
-        <f>AVERAGE(M9:N9)</f>
-        <v>31</v>
-      </c>
-      <c r="T9">
-        <f>AVERAGE(Q9:S9)</f>
-        <v>23.5</v>
-      </c>
-      <c r="U9">
-        <f>MIN(Q9:S9)</f>
-        <v>19</v>
-      </c>
-      <c r="V9">
-        <f>T9-U9</f>
-        <v>4.5</v>
-      </c>
-      <c r="W9">
-        <f>AVERAGE(Q9:Q12)</f>
-        <v>17.75</v>
-      </c>
-      <c r="X9">
-        <f>_xlfn.STDEV.S(Q9:Q11)</f>
-        <v>2.3094010767584989</v>
-      </c>
-      <c r="Y9">
-        <f>AVERAGE(R9:R11)</f>
-        <v>21.333333333333332</v>
-      </c>
-      <c r="Z9">
-        <f>_xlfn.STDEV.S(R9:R11)</f>
-        <v>2.84312035153867</v>
-      </c>
-      <c r="AA9">
-        <f>AVERAGE(S9:S11)</f>
-        <v>32</v>
-      </c>
-      <c r="AB9">
-        <f>_xlfn.STDEV.S(S9:S11)</f>
-        <v>1.3228756555322954</v>
-      </c>
-      <c r="AC9">
-        <f>AVERAGE(T9:T11)</f>
-        <v>23.722222222222218</v>
-      </c>
-      <c r="AD9">
-        <f>_xlfn.STDEV.S(T9:T11)</f>
-        <v>1.0183501544346309</v>
-      </c>
-      <c r="AE9">
-        <f>AVERAGE(V9:V11)</f>
-        <v>6.3888888888888884</v>
-      </c>
-      <c r="AF9">
-        <f>_xlfn.STDEV.S(V9:V11)</f>
-        <v>1.9172704363041528</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>84</v>
-      </c>
-      <c r="C10">
-        <v>16</v>
-      </c>
-      <c r="D10">
-        <v>17</v>
-      </c>
-      <c r="E10">
-        <v>83</v>
-      </c>
-      <c r="G10">
-        <v>58</v>
-      </c>
-      <c r="H10">
-        <v>42</v>
-      </c>
-      <c r="I10">
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>79</v>
+      </c>
+      <c r="G8">
+        <v>71</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
         <v>7</v>
       </c>
-      <c r="J10">
+      <c r="J8">
         <v>93</v>
       </c>
-      <c r="L10">
-        <v>51</v>
-      </c>
-      <c r="M10">
-        <v>49</v>
-      </c>
-      <c r="N10">
+      <c r="L8">
+        <v>71</v>
+      </c>
+      <c r="M8">
+        <v>29</v>
+      </c>
+      <c r="N8">
+        <v>21</v>
+      </c>
+      <c r="O8">
+        <v>79</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="O10">
-        <v>82</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" ref="Q10:Q12" si="4">AVERAGE(C10:D10)</f>
-        <v>16.5</v>
-      </c>
-      <c r="R10">
-        <f t="shared" ref="R10:R12" si="5">AVERAGE(H10:I10)</f>
-        <v>24.5</v>
-      </c>
-      <c r="S10">
-        <f t="shared" ref="S10:S12" si="6">AVERAGE(M10:N10)</f>
-        <v>33.5</v>
-      </c>
-      <c r="T10">
-        <f t="shared" ref="T10:T12" si="7">AVERAGE(Q10:S10)</f>
-        <v>24.833333333333332</v>
-      </c>
-      <c r="U10">
-        <f>MIN(Q10:S10)</f>
-        <v>16.5</v>
-      </c>
-      <c r="V10">
-        <f>T10-U10</f>
-        <v>8.3333333333333321</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>82</v>
-      </c>
-      <c r="C11">
-        <v>18</v>
-      </c>
-      <c r="D11">
+      <c r="S8">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="7"/>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="E11">
-        <v>85</v>
-      </c>
-      <c r="G11">
-        <v>64</v>
-      </c>
-      <c r="H11">
-        <v>36</v>
-      </c>
-      <c r="I11">
-        <v>5</v>
-      </c>
-      <c r="J11">
-        <v>95</v>
-      </c>
-      <c r="L11">
-        <v>69</v>
-      </c>
-      <c r="M11">
-        <v>31</v>
-      </c>
-      <c r="N11">
-        <v>32</v>
-      </c>
-      <c r="O11">
-        <v>68</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="4"/>
-        <v>16.5</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="5"/>
-        <v>20.5</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="6"/>
-        <v>31.5</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="7"/>
-        <v>22.833333333333332</v>
-      </c>
-      <c r="U11">
-        <f>MIN(Q11:S11)</f>
-        <v>16.5</v>
-      </c>
-      <c r="V11">
-        <f>T11-U11</f>
-        <v>6.3333333333333321</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>78</v>
-      </c>
-      <c r="C12">
-        <v>22</v>
-      </c>
-      <c r="D12">
-        <v>13</v>
-      </c>
-      <c r="E12">
-        <v>87</v>
-      </c>
-      <c r="G12">
-        <v>57</v>
-      </c>
-      <c r="H12">
-        <v>43</v>
-      </c>
-      <c r="I12">
-        <v>7</v>
-      </c>
-      <c r="J12">
-        <v>93</v>
-      </c>
-      <c r="L12">
-        <v>67</v>
-      </c>
-      <c r="M12">
-        <v>33</v>
-      </c>
-      <c r="N12">
-        <v>26</v>
-      </c>
-      <c r="O12">
-        <v>74</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="4"/>
-        <v>17.5</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="6"/>
-        <v>29.5</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="7"/>
-        <v>24</v>
-      </c>
-      <c r="U12">
-        <f>MIN(Q12:S12)</f>
-        <v>17.5</v>
-      </c>
-      <c r="V12">
-        <f>T12-U12</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>80</v>
-      </c>
-      <c r="C15">
-        <v>20</v>
-      </c>
-      <c r="D15">
-        <v>18</v>
-      </c>
-      <c r="E15">
-        <v>82</v>
-      </c>
-      <c r="G15">
-        <v>56</v>
-      </c>
-      <c r="H15">
-        <v>44</v>
-      </c>
-      <c r="I15">
-        <v>8</v>
-      </c>
-      <c r="J15">
-        <v>92</v>
-      </c>
-      <c r="L15">
-        <v>67</v>
-      </c>
-      <c r="M15">
-        <v>33</v>
-      </c>
-      <c r="N15">
-        <v>21</v>
-      </c>
-      <c r="O15">
-        <v>79</v>
-      </c>
-      <c r="Q15">
-        <f>AVERAGE(C15:D15)</f>
-        <v>19</v>
-      </c>
-      <c r="R15">
-        <f>AVERAGE(H15:I15)</f>
-        <v>26</v>
-      </c>
-      <c r="S15">
-        <f>AVERAGE(M15:N15)</f>
-        <v>27</v>
-      </c>
-      <c r="T15">
-        <f>AVERAGE(Q15:S15)</f>
-        <v>24</v>
-      </c>
-      <c r="U15">
-        <f>MIN(Q15:S15)</f>
-        <v>19</v>
-      </c>
-      <c r="V15">
-        <f>T15-U15</f>
-        <v>5</v>
-      </c>
-      <c r="W15">
-        <f>AVERAGE(Q15:Q18)</f>
-        <v>15.25</v>
-      </c>
-      <c r="X15">
-        <f>_xlfn.STDEV.S(Q15:Q17)</f>
-        <v>5.3033008588991066</v>
-      </c>
-      <c r="Y15">
-        <f>AVERAGE(R15:R17)</f>
-        <v>24.25</v>
-      </c>
-      <c r="Z15">
-        <f>_xlfn.STDEV.S(R15:R17)</f>
-        <v>2.4748737341529163</v>
-      </c>
-      <c r="AA15">
-        <f>AVERAGE(S15:S17)</f>
-        <v>28</v>
-      </c>
-      <c r="AB15">
-        <f>_xlfn.STDEV.S(S15:S17)</f>
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="AC15">
-        <f>AVERAGE(T15:T17)</f>
-        <v>22.5</v>
-      </c>
-      <c r="AD15">
-        <f>_xlfn.STDEV.S(T15:T17)</f>
-        <v>2.1213203435596424</v>
-      </c>
-      <c r="AE15">
-        <f>AVERAGE(V15:V17)</f>
-        <v>7.25</v>
-      </c>
-      <c r="AF15">
-        <f>_xlfn.STDEV.S(V15:V17)</f>
-        <v>3.1819805153394638</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B16">
-        <v>85</v>
-      </c>
-      <c r="C16">
-        <v>15</v>
-      </c>
-      <c r="D16">
-        <v>8</v>
-      </c>
-      <c r="E16">
-        <v>92</v>
-      </c>
-      <c r="G16">
-        <v>58</v>
-      </c>
-      <c r="H16">
-        <v>42</v>
-      </c>
-      <c r="I16">
-        <v>3</v>
-      </c>
-      <c r="J16">
-        <v>97</v>
-      </c>
-      <c r="L16">
-        <v>67</v>
-      </c>
-      <c r="M16">
-        <v>33</v>
-      </c>
-      <c r="N16">
-        <v>25</v>
-      </c>
-      <c r="O16">
-        <v>75</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" ref="Q16" si="8">AVERAGE(C16:D16)</f>
-        <v>11.5</v>
-      </c>
-      <c r="R16">
-        <f t="shared" ref="R16" si="9">AVERAGE(H16:I16)</f>
-        <v>22.5</v>
-      </c>
-      <c r="S16">
-        <f t="shared" ref="S16" si="10">AVERAGE(M16:N16)</f>
-        <v>29</v>
-      </c>
-      <c r="T16">
-        <f t="shared" ref="T16" si="11">AVERAGE(Q16:S16)</f>
-        <v>21</v>
-      </c>
-      <c r="U16">
-        <f>MIN(Q16:S16)</f>
-        <v>11.5</v>
-      </c>
-      <c r="V16">
-        <f>T16-U16</f>
-        <v>9.5</v>
+      <c r="V8">
+        <f t="shared" si="9"/>
+        <v>4.3333333333333321</v>
       </c>
     </row>
   </sheetData>
